--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0118.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0118.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Ha! Vậy là… cậu đã chính thức bóc mẽ thêm một truyền thuyết đô thị nữa rồi.</t>
+          <t>Ha! Vậy là… mày đã chính thức bóc mẽ thêm một truyền thuyết đô thị nữa rồi.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Đừng có mà bảo cậu lại đi tạo ra những truyền thuyết đô thị đấy nhé.</t>
+          <t>Đừng có mà bảo mày lại đi tạo ra những truyền thuyết đô thị đấy nhé.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dù sao thì dù là Mindbending Herder hay thứ gì khác, nếu gặp phải huyền thoại đô thị nào nữa thì cứ gọi ta bất cứ lúc nào!</t>
+          <t>Dù sao thì dù là Mindbending Herder hay thứ gì khác, nếu gặp phải huyền thoại đô thị nào nữa thì cứ gọi tao bất cứ lúc nào!</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Tối quá. Ta không tìm thấy đồ của mình nữa… Lại đây, lại giúp ta với…</t>
+          <t>Tối quá. Tao không tìm thấy đồ của mình nữa… Lại đây, lại giúp tao với…</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Ai... Không, cậu &lt;i&gt;là cái gì&lt;/i&gt; vậy?</t>
+          <t>Ai... Không, mày &lt;i&gt;là cái gì&lt;/i&gt; vậy?</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Sao cậu ấy không đến thăm ta nữa… và lại nở nụ cười ấy với người khác?</t>
+          <t>Sao cậu ấy không đến thăm tao nữa… và lại nở nụ cười ấy với người khác?</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Trước đây, ta đã coi việc này là phí thời gian.</t>
+          <t>Trước đây, tao đã coi việc này là phí thời gian.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Đó là cái giá ta đã nói. Giờ thì đi thôi.</t>
+          <t>Đó là cái giá tao đã nói. Giờ thì đi thôi.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Và khi xem lại những ví dụ về tình yêu trong cơ sở dữ liệu, ta tự đặt mình vào vị trí của họ.</t>
+          <t>Và khi xem lại những ví dụ về tình yêu trong cơ sở dữ liệu, tao tự đặt mình vào vị trí của họ.</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Nước với ta cứ nhớp nháp, nhớt nhớt thế nào ấy.</t>
+          <t>Nước với tao cứ nhớp nháp, nhớt nhớt thế nào ấy.</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Ta nghe lén tụi ngươi nói chuyện về xe máy.</t>
+          <t>Tao nghe lén tụi mày nói chuyện về xe máy.</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Ai cũng hỏi thế! Vì vậy... giờ chỉ còn mình em gái và ta thôi.</t>
+          <t>Ai cũng hỏi thế! Vì vậy... giờ chỉ còn mình em gái và tao thôi.</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Ta muốn thu thập dữ liệu về con đường mới, nhưng ta không tự lái xe máy được. Vậy nên cần ai đó chạy thử một vòng.</t>
+          <t>Tao muốn thu thập dữ liệu về con đường mới, nhưng tao không tự lái xe máy được. Vậy nên cần ai đó chạy thử một vòng.</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Ta sẽ thử.</t>
+          <t>Tao sẽ thử.</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nếu thấy ta đang ngươi mò cái gì đó, ghé qua chào nhé!</t>
+          <t>Nếu thấy ta đang mày mò cái gì đó, ghé qua chào nhé!</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Ta nhớ ngươi.</t>
+          <t>Tao nhớ mày.</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Về cơ bản, đây là vấn đề quan trọng thứ hai sau nghiên cứu của chúng ta, nên để ta lo phần giới thiệu cô ấy nhé.</t>
+          <t>Về cơ bản, đây là vấn đề quan trọng thứ hai sau nghiên cứu của chúng ta, nên để tao lo phần giới thiệu cô ấy nhé.</t>
         </is>
       </c>
     </row>
@@ -28069,7 +28069,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Ôi, {PlayerName}! Ta thấy kỹ năng lái của ngươi tiến bộ hẳn!</t>
+          <t>Ôi, {PlayerName}! Tao thấy kỹ năng lái của mày tiến bộ hẳn!</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Ôi, {PlayerName}! Ta thấy kỹ năng lái của ngươi tiến bộ hẳn!</t>
+          <t>Ôi, {PlayerName}! Tao thấy kỹ năng lái của mày tiến bộ hẳn!</t>
         </is>
       </c>
     </row>
